--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF ROLANDO 441/excel.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF ROLANDO 441/excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AGS\DESARROLLO\GITHUB\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF ROLANDO 441\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DB284C-8600-4B70-A610-B7112477EBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68B1D2E-12BE-4D53-B772-69ECF1A89E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3345,7 +3345,7 @@
         <v>48</v>
       </c>
       <c r="C2" s="29">
-        <v>16.166666666666668</v>
+        <v>16</v>
       </c>
       <c r="D2" s="29">
         <v>5</v>
@@ -3715,7 +3715,7 @@
         <v>340</v>
       </c>
       <c r="C7" s="29">
-        <v>89.596590909090907</v>
+        <v>90</v>
       </c>
       <c r="D7" s="29">
         <v>1</v>
@@ -3863,7 +3863,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="29">
-        <v>5.1111111111111107</v>
+        <v>5</v>
       </c>
       <c r="D9" s="29">
         <v>5</v>
@@ -3937,7 +3937,7 @@
         <v>65</v>
       </c>
       <c r="C10" s="29">
-        <v>19.382978723404257</v>
+        <v>19</v>
       </c>
       <c r="D10" s="29">
         <v>5</v>
@@ -4159,7 +4159,7 @@
         <v>310</v>
       </c>
       <c r="C13" s="29">
-        <v>24.076923076923077</v>
+        <v>24</v>
       </c>
       <c r="D13" s="29">
         <v>5</v>
@@ -4233,7 +4233,7 @@
         <v>336</v>
       </c>
       <c r="C14" s="29">
-        <v>111.64285714285714</v>
+        <v>112</v>
       </c>
       <c r="D14" s="29">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>369</v>
       </c>
       <c r="C15" s="29">
-        <v>31.875</v>
+        <v>32</v>
       </c>
       <c r="D15" s="29">
         <v>4</v>
@@ -4381,7 +4381,7 @@
         <v>372</v>
       </c>
       <c r="C16" s="29">
-        <v>148.25</v>
+        <v>148</v>
       </c>
       <c r="D16" s="29">
         <v>1</v>
@@ -4751,7 +4751,7 @@
         <v>78</v>
       </c>
       <c r="C21" s="29">
-        <v>11.343096234309623</v>
+        <v>11</v>
       </c>
       <c r="D21" s="29">
         <v>5</v>
@@ -4825,7 +4825,7 @@
         <v>142</v>
       </c>
       <c r="C22" s="29">
-        <v>66.8</v>
+        <v>67</v>
       </c>
       <c r="D22" s="29">
         <v>1</v>
@@ -4899,7 +4899,7 @@
         <v>270</v>
       </c>
       <c r="C23" s="29">
-        <v>83.166077738515895</v>
+        <v>83</v>
       </c>
       <c r="D23" s="29">
         <v>1</v>
@@ -5121,7 +5121,7 @@
         <v>283</v>
       </c>
       <c r="C26" s="29">
-        <v>54.970588235294116</v>
+        <v>55</v>
       </c>
       <c r="D26" s="29">
         <v>2</v>
@@ -5269,7 +5269,7 @@
         <v>346</v>
       </c>
       <c r="C28" s="29">
-        <v>10.262295081967213</v>
+        <v>10</v>
       </c>
       <c r="D28" s="29">
         <v>5</v>
@@ -5417,7 +5417,7 @@
         <v>201</v>
       </c>
       <c r="C30" s="29">
-        <v>53.156626506024097</v>
+        <v>53</v>
       </c>
       <c r="D30" s="29">
         <v>2</v>
@@ -5639,7 +5639,7 @@
         <v>397</v>
       </c>
       <c r="C33" s="29">
-        <v>24.129032258064516</v>
+        <v>24</v>
       </c>
       <c r="D33" s="29">
         <v>5</v>
@@ -5787,7 +5787,7 @@
         <v>396</v>
       </c>
       <c r="C35" s="29">
-        <v>10.368421052631579</v>
+        <v>10</v>
       </c>
       <c r="D35" s="29">
         <v>5</v>
@@ -5861,7 +5861,7 @@
         <v>185</v>
       </c>
       <c r="C36" s="29">
-        <v>23.761904761904763</v>
+        <v>24</v>
       </c>
       <c r="D36" s="29">
         <v>5</v>
@@ -5935,7 +5935,7 @@
         <v>263</v>
       </c>
       <c r="C37" s="29">
-        <v>13.333333333333334</v>
+        <v>13</v>
       </c>
       <c r="D37" s="29">
         <v>5</v>
@@ -6083,7 +6083,7 @@
         <v>402</v>
       </c>
       <c r="C39" s="29">
-        <v>23.19047619047619</v>
+        <v>23</v>
       </c>
       <c r="D39" s="29">
         <v>5</v>
@@ -6231,7 +6231,7 @@
         <v>394</v>
       </c>
       <c r="C41" s="29">
-        <v>10.217391304347826</v>
+        <v>10</v>
       </c>
       <c r="D41" s="29">
         <v>5</v>
@@ -6305,7 +6305,7 @@
         <v>16</v>
       </c>
       <c r="C42" s="29">
-        <v>52.727272727272727</v>
+        <v>53</v>
       </c>
       <c r="D42" s="29">
         <v>2</v>
@@ -6601,7 +6601,7 @@
         <v>115</v>
       </c>
       <c r="C46" s="29">
-        <v>24.90909090909091</v>
+        <v>25</v>
       </c>
       <c r="D46" s="29">
         <v>5</v>
@@ -6675,7 +6675,7 @@
         <v>97</v>
       </c>
       <c r="C47" s="29">
-        <v>59.4</v>
+        <v>59</v>
       </c>
       <c r="D47" s="29">
         <v>2</v>
@@ -6749,7 +6749,7 @@
         <v>99</v>
       </c>
       <c r="C48" s="29">
-        <v>3.3333333333333335</v>
+        <v>3</v>
       </c>
       <c r="D48" s="29">
         <v>5</v>
@@ -6897,7 +6897,7 @@
         <v>125</v>
       </c>
       <c r="C50" s="29">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="D50" s="29">
         <v>5</v>
@@ -7119,7 +7119,7 @@
         <v>109</v>
       </c>
       <c r="C53" s="29">
-        <v>17.565217391304348</v>
+        <v>18</v>
       </c>
       <c r="D53" s="29">
         <v>5</v>
@@ -7193,7 +7193,7 @@
         <v>183</v>
       </c>
       <c r="C54" s="29">
-        <v>11.050167224080267</v>
+        <v>11</v>
       </c>
       <c r="D54" s="29">
         <v>5</v>
@@ -7563,7 +7563,7 @@
         <v>143</v>
       </c>
       <c r="C59" s="29">
-        <v>33.375</v>
+        <v>33</v>
       </c>
       <c r="D59" s="29">
         <v>4</v>
@@ -7785,7 +7785,7 @@
         <v>202</v>
       </c>
       <c r="C62" s="29">
-        <v>32.785714285714285</v>
+        <v>33</v>
       </c>
       <c r="D62" s="29">
         <v>4</v>
@@ -7933,7 +7933,7 @@
         <v>209</v>
       </c>
       <c r="C64" s="29">
-        <v>62.75</v>
+        <v>63</v>
       </c>
       <c r="D64" s="29">
         <v>1</v>
@@ -8081,7 +8081,7 @@
         <v>273</v>
       </c>
       <c r="C66" s="29">
-        <v>60.323170731707314</v>
+        <v>60</v>
       </c>
       <c r="D66" s="29">
         <v>1</v>
@@ -8303,7 +8303,7 @@
         <v>347</v>
       </c>
       <c r="C69" s="29">
-        <v>22.46153846153846</v>
+        <v>22</v>
       </c>
       <c r="D69" s="29">
         <v>5</v>
@@ -8377,7 +8377,7 @@
         <v>114</v>
       </c>
       <c r="C70" s="29">
-        <v>12.333333333333334</v>
+        <v>12</v>
       </c>
       <c r="D70" s="29">
         <v>5</v>
@@ -8747,7 +8747,7 @@
         <v>370</v>
       </c>
       <c r="C75" s="29">
-        <v>27.666666666666668</v>
+        <v>28</v>
       </c>
       <c r="D75" s="29">
         <v>5</v>
@@ -9117,7 +9117,7 @@
         <v>390</v>
       </c>
       <c r="C80" s="29">
-        <v>12.222222222222221</v>
+        <v>12</v>
       </c>
       <c r="D80" s="29">
         <v>5</v>
@@ -9413,7 +9413,7 @@
         <v>407</v>
       </c>
       <c r="C84" s="29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="D84" s="29">
         <v>5</v>
@@ -9635,7 +9635,7 @@
         <v>66</v>
       </c>
       <c r="C87" s="29">
-        <v>27.583333333333332</v>
+        <v>28</v>
       </c>
       <c r="D87" s="29">
         <v>5</v>
@@ -9709,7 +9709,7 @@
         <v>68</v>
       </c>
       <c r="C88" s="29">
-        <v>34.06818181818182</v>
+        <v>34</v>
       </c>
       <c r="D88" s="29">
         <v>4</v>
@@ -9783,7 +9783,7 @@
         <v>70</v>
       </c>
       <c r="C89" s="29">
-        <v>16.666666666666668</v>
+        <v>17</v>
       </c>
       <c r="D89" s="29">
         <v>5</v>
@@ -9857,7 +9857,7 @@
         <v>71</v>
       </c>
       <c r="C90" s="29">
-        <v>8.5294117647058822</v>
+        <v>9</v>
       </c>
       <c r="D90" s="29">
         <v>5</v>
@@ -10079,7 +10079,7 @@
         <v>76</v>
       </c>
       <c r="C93" s="29">
-        <v>33.533333333333331</v>
+        <v>34</v>
       </c>
       <c r="D93" s="29">
         <v>4</v>
@@ -10227,7 +10227,7 @@
         <v>79</v>
       </c>
       <c r="C95" s="29">
-        <v>8.6666666666666661</v>
+        <v>9</v>
       </c>
       <c r="D95" s="29">
         <v>5</v>
@@ -10671,7 +10671,7 @@
         <v>88</v>
       </c>
       <c r="C101" s="29">
-        <v>114.4</v>
+        <v>114</v>
       </c>
       <c r="D101" s="29">
         <v>1</v>
@@ -10893,7 +10893,7 @@
         <v>96</v>
       </c>
       <c r="C104" s="29">
-        <v>10.192307692307692</v>
+        <v>10</v>
       </c>
       <c r="D104" s="29">
         <v>5</v>
@@ -11041,7 +11041,7 @@
         <v>104</v>
       </c>
       <c r="C106" s="29">
-        <v>32.569620253164558</v>
+        <v>33</v>
       </c>
       <c r="D106" s="29">
         <v>4</v>
@@ -11189,7 +11189,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="29">
-        <v>12.555555555555555</v>
+        <v>13</v>
       </c>
       <c r="D108" s="29">
         <v>5</v>
@@ -11337,7 +11337,7 @@
         <v>117</v>
       </c>
       <c r="C110" s="29">
-        <v>26.016949152542374</v>
+        <v>26</v>
       </c>
       <c r="D110" s="29">
         <v>5</v>
@@ -11411,7 +11411,7 @@
         <v>118</v>
       </c>
       <c r="C111" s="29">
-        <v>106.83076923076923</v>
+        <v>107</v>
       </c>
       <c r="D111" s="29">
         <v>1</v>
@@ -11485,7 +11485,7 @@
         <v>121</v>
       </c>
       <c r="C112" s="29">
-        <v>38.410256410256409</v>
+        <v>38</v>
       </c>
       <c r="D112" s="29">
         <v>4</v>
@@ -11633,7 +11633,7 @@
         <v>126</v>
       </c>
       <c r="C114" s="29">
-        <v>6.6645161290322577</v>
+        <v>7</v>
       </c>
       <c r="D114" s="29">
         <v>5</v>
@@ -11707,7 +11707,7 @@
         <v>129</v>
       </c>
       <c r="C115" s="29">
-        <v>153.58823529411765</v>
+        <v>154</v>
       </c>
       <c r="D115" s="29">
         <v>1</v>
@@ -11781,7 +11781,7 @@
         <v>130</v>
       </c>
       <c r="C116" s="29">
-        <v>51.155963302752291</v>
+        <v>51</v>
       </c>
       <c r="D116" s="29">
         <v>2</v>
@@ -11929,7 +11929,7 @@
         <v>134</v>
       </c>
       <c r="C118" s="29">
-        <v>21.714285714285715</v>
+        <v>22</v>
       </c>
       <c r="D118" s="29">
         <v>5</v>
@@ -12003,7 +12003,7 @@
         <v>141</v>
       </c>
       <c r="C119" s="29">
-        <v>18.62962962962963</v>
+        <v>19</v>
       </c>
       <c r="D119" s="29">
         <v>5</v>
@@ -12151,7 +12151,7 @@
         <v>157</v>
       </c>
       <c r="C121" s="29">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="D121" s="29">
         <v>4</v>
@@ -12299,7 +12299,7 @@
         <v>169</v>
       </c>
       <c r="C123" s="29">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="D123" s="29">
         <v>2</v>
@@ -12373,7 +12373,7 @@
         <v>20</v>
       </c>
       <c r="C124" s="29">
-        <v>23.612765957446808</v>
+        <v>24</v>
       </c>
       <c r="D124" s="29">
         <v>5</v>
@@ -12447,7 +12447,7 @@
         <v>30</v>
       </c>
       <c r="C125" s="29">
-        <v>17.625</v>
+        <v>18</v>
       </c>
       <c r="D125" s="29">
         <v>5</v>
@@ -12521,7 +12521,7 @@
         <v>32</v>
       </c>
       <c r="C126" s="29">
-        <v>44.098039215686278</v>
+        <v>44</v>
       </c>
       <c r="D126" s="29">
         <v>3</v>
@@ -12595,7 +12595,7 @@
         <v>38</v>
       </c>
       <c r="C127" s="29">
-        <v>45.25</v>
+        <v>45</v>
       </c>
       <c r="D127" s="29">
         <v>3</v>
@@ -12669,7 +12669,7 @@
         <v>43</v>
       </c>
       <c r="C128" s="29">
-        <v>23.857142857142858</v>
+        <v>24</v>
       </c>
       <c r="D128" s="29">
         <v>5</v>
@@ -12817,7 +12817,7 @@
         <v>44</v>
       </c>
       <c r="C130" s="29">
-        <v>48.727272727272727</v>
+        <v>49</v>
       </c>
       <c r="D130" s="29">
         <v>3</v>
@@ -12965,7 +12965,7 @@
         <v>100</v>
       </c>
       <c r="C132" s="29">
-        <v>52.802030456852791</v>
+        <v>53</v>
       </c>
       <c r="D132" s="29">
         <v>2</v>
@@ -13039,7 +13039,7 @@
         <v>105</v>
       </c>
       <c r="C133" s="29">
-        <v>19.059322033898304</v>
+        <v>19</v>
       </c>
       <c r="D133" s="29">
         <v>5</v>
@@ -13187,7 +13187,7 @@
         <v>155</v>
       </c>
       <c r="C135" s="29">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="D135" s="29">
         <v>5</v>
@@ -13261,7 +13261,7 @@
         <v>154</v>
       </c>
       <c r="C136" s="29">
-        <v>25.638888888888889</v>
+        <v>26</v>
       </c>
       <c r="D136" s="29">
         <v>5</v>
@@ -13335,7 +13335,7 @@
         <v>163</v>
       </c>
       <c r="C137" s="29">
-        <v>29.247557003257327</v>
+        <v>29</v>
       </c>
       <c r="D137" s="29">
         <v>5</v>
@@ -13483,7 +13483,7 @@
         <v>166</v>
       </c>
       <c r="C139" s="29">
-        <v>31.863636363636363</v>
+        <v>32</v>
       </c>
       <c r="D139" s="29">
         <v>4</v>
@@ -13705,7 +13705,7 @@
         <v>173</v>
       </c>
       <c r="C142" s="29">
-        <v>74.948571428571427</v>
+        <v>75</v>
       </c>
       <c r="D142" s="29">
         <v>1</v>
@@ -13779,7 +13779,7 @@
         <v>174</v>
       </c>
       <c r="C143" s="29">
-        <v>6.333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D143" s="29">
         <v>5</v>
@@ -13927,7 +13927,7 @@
         <v>194</v>
       </c>
       <c r="C145" s="29">
-        <v>177.27891156462584</v>
+        <v>177</v>
       </c>
       <c r="D145" s="29">
         <v>1</v>
@@ -14149,7 +14149,7 @@
         <v>206</v>
       </c>
       <c r="C148" s="29">
-        <v>31.153846153846153</v>
+        <v>31</v>
       </c>
       <c r="D148" s="29">
         <v>4</v>
@@ -14223,7 +14223,7 @@
         <v>207</v>
       </c>
       <c r="C149" s="29">
-        <v>24.666666666666668</v>
+        <v>25</v>
       </c>
       <c r="D149" s="29">
         <v>5</v>
@@ -14297,7 +14297,7 @@
         <v>216</v>
       </c>
       <c r="C150" s="29">
-        <v>28.523809523809526</v>
+        <v>29</v>
       </c>
       <c r="D150" s="29">
         <v>5</v>
@@ -14445,7 +14445,7 @@
         <v>232</v>
       </c>
       <c r="C152" s="29">
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="D152" s="29">
         <v>1</v>
@@ -14519,7 +14519,7 @@
         <v>240</v>
       </c>
       <c r="C153" s="29">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="D153" s="29">
         <v>5</v>
@@ -14963,7 +14963,7 @@
         <v>289</v>
       </c>
       <c r="C159" s="29">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="D159" s="29">
         <v>5</v>
@@ -15407,7 +15407,7 @@
         <v>334</v>
       </c>
       <c r="C165" s="29">
-        <v>16.433333333333334</v>
+        <v>16</v>
       </c>
       <c r="D165" s="29">
         <v>5</v>
@@ -15925,7 +15925,7 @@
         <v>45</v>
       </c>
       <c r="C172" s="29">
-        <v>76.426966292134836</v>
+        <v>76</v>
       </c>
       <c r="D172" s="29">
         <v>1</v>
@@ -16221,7 +16221,7 @@
         <v>63</v>
       </c>
       <c r="C176" s="29">
-        <v>11.162162162162161</v>
+        <v>11</v>
       </c>
       <c r="D176" s="29">
         <v>5</v>
@@ -16295,7 +16295,7 @@
         <v>64</v>
       </c>
       <c r="C177" s="29">
-        <v>43.92</v>
+        <v>44</v>
       </c>
       <c r="D177" s="29">
         <v>3</v>
@@ -16369,7 +16369,7 @@
         <v>73</v>
       </c>
       <c r="C178" s="29">
-        <v>13.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="D178" s="29">
         <v>5</v>
@@ -16591,7 +16591,7 @@
         <v>89</v>
       </c>
       <c r="C181" s="29">
-        <v>42.230769230769234</v>
+        <v>42</v>
       </c>
       <c r="D181" s="29">
         <v>3</v>
@@ -16665,7 +16665,7 @@
         <v>92</v>
       </c>
       <c r="C182" s="29">
-        <v>34.620689655172413</v>
+        <v>35</v>
       </c>
       <c r="D182" s="29">
         <v>4</v>
@@ -16813,7 +16813,7 @@
         <v>116</v>
       </c>
       <c r="C184" s="29">
-        <v>202.5</v>
+        <v>203</v>
       </c>
       <c r="D184" s="29">
         <v>1</v>
@@ -16887,7 +16887,7 @@
         <v>128</v>
       </c>
       <c r="C185" s="29">
-        <v>39.19047619047619</v>
+        <v>39</v>
       </c>
       <c r="D185" s="29">
         <v>4</v>
@@ -16961,7 +16961,7 @@
         <v>144</v>
       </c>
       <c r="C186" s="29">
-        <v>55.666666666666664</v>
+        <v>56</v>
       </c>
       <c r="D186" s="29">
         <v>2</v>
@@ -17035,7 +17035,7 @@
         <v>148</v>
       </c>
       <c r="C187" s="29">
-        <v>3.1176470588235294</v>
+        <v>3</v>
       </c>
       <c r="D187" s="29">
         <v>5</v>
@@ -17109,7 +17109,7 @@
         <v>149</v>
       </c>
       <c r="C188" s="29">
-        <v>29.833333333333332</v>
+        <v>30</v>
       </c>
       <c r="D188" s="29">
         <v>5</v>
@@ -17257,7 +17257,7 @@
         <v>159</v>
       </c>
       <c r="C190" s="29">
-        <v>8.125</v>
+        <v>8</v>
       </c>
       <c r="D190" s="29">
         <v>5</v>
@@ -17331,7 +17331,7 @@
         <v>161</v>
       </c>
       <c r="C191" s="29">
-        <v>19.071428571428573</v>
+        <v>19</v>
       </c>
       <c r="D191" s="29">
         <v>5</v>
@@ -17479,7 +17479,7 @@
         <v>178</v>
       </c>
       <c r="C193" s="29">
-        <v>36.18181818181818</v>
+        <v>36</v>
       </c>
       <c r="D193" s="29">
         <v>4</v>
@@ -17701,7 +17701,7 @@
         <v>192</v>
       </c>
       <c r="C196" s="29">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="D196" s="29">
         <v>5</v>
@@ -17775,7 +17775,7 @@
         <v>198</v>
       </c>
       <c r="C197" s="29">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="D197" s="29">
         <v>5</v>
@@ -17923,7 +17923,7 @@
         <v>200</v>
       </c>
       <c r="C199" s="29">
-        <v>12.461538461538462</v>
+        <v>12</v>
       </c>
       <c r="D199" s="29">
         <v>5</v>
@@ -18145,7 +18145,7 @@
         <v>213</v>
       </c>
       <c r="C202" s="29">
-        <v>26.621052631578948</v>
+        <v>27</v>
       </c>
       <c r="D202" s="29">
         <v>5</v>
@@ -18293,7 +18293,7 @@
         <v>217</v>
       </c>
       <c r="C204" s="29">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="D204" s="29">
         <v>4</v>
@@ -18515,7 +18515,7 @@
         <v>222</v>
       </c>
       <c r="C207" s="29">
-        <v>22.520833333333332</v>
+        <v>23</v>
       </c>
       <c r="D207" s="29">
         <v>5</v>
@@ -18737,7 +18737,7 @@
         <v>244</v>
       </c>
       <c r="C210" s="29">
-        <v>28.333333333333332</v>
+        <v>28</v>
       </c>
       <c r="D210" s="29">
         <v>5</v>
@@ -18811,7 +18811,7 @@
         <v>264</v>
       </c>
       <c r="C211" s="29">
-        <v>46.238095238095241</v>
+        <v>46</v>
       </c>
       <c r="D211" s="29">
         <v>3</v>
@@ -18959,7 +18959,7 @@
         <v>249</v>
       </c>
       <c r="C213" s="29">
-        <v>27.76</v>
+        <v>28</v>
       </c>
       <c r="D213" s="29">
         <v>5</v>
@@ -19033,7 +19033,7 @@
         <v>266</v>
       </c>
       <c r="C214" s="29">
-        <v>14.727272727272727</v>
+        <v>15</v>
       </c>
       <c r="D214" s="29">
         <v>5</v>
@@ -19181,7 +19181,7 @@
         <v>257</v>
       </c>
       <c r="C216" s="29">
-        <v>23.551724137931036</v>
+        <v>24</v>
       </c>
       <c r="D216" s="29">
         <v>5</v>
@@ -19255,7 +19255,7 @@
         <v>259</v>
       </c>
       <c r="C217" s="29">
-        <v>39.930232558139537</v>
+        <v>40</v>
       </c>
       <c r="D217" s="29">
         <v>4</v>
@@ -19329,7 +19329,7 @@
         <v>246</v>
       </c>
       <c r="C218" s="29">
-        <v>56.333333333333336</v>
+        <v>56</v>
       </c>
       <c r="D218" s="29">
         <v>2</v>
@@ -19477,7 +19477,7 @@
         <v>288</v>
       </c>
       <c r="C220" s="29">
-        <v>38.337662337662337</v>
+        <v>38</v>
       </c>
       <c r="D220" s="29">
         <v>4</v>
@@ -19847,7 +19847,7 @@
         <v>306</v>
       </c>
       <c r="C225" s="29">
-        <v>55.833333333333336</v>
+        <v>56</v>
       </c>
       <c r="D225" s="29">
         <v>2</v>
@@ -19921,7 +19921,7 @@
         <v>274</v>
       </c>
       <c r="C226" s="29">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="D226" s="29">
         <v>5</v>
@@ -20439,7 +20439,7 @@
         <v>298</v>
       </c>
       <c r="C233" s="29">
-        <v>93.92307692307692</v>
+        <v>94</v>
       </c>
       <c r="D233" s="29">
         <v>1</v>
@@ -20513,7 +20513,7 @@
         <v>301</v>
       </c>
       <c r="C234" s="29">
-        <v>5.9268292682926829</v>
+        <v>6</v>
       </c>
       <c r="D234" s="29">
         <v>5</v>
@@ -20587,7 +20587,7 @@
         <v>309</v>
       </c>
       <c r="C235" s="29">
-        <v>24.12</v>
+        <v>24</v>
       </c>
       <c r="D235" s="29">
         <v>5</v>
@@ -20735,7 +20735,7 @@
         <v>294</v>
       </c>
       <c r="C237" s="29">
-        <v>163.2340425531915</v>
+        <v>163</v>
       </c>
       <c r="D237" s="29">
         <v>1</v>
@@ -20809,7 +20809,7 @@
         <v>364</v>
       </c>
       <c r="C238" s="29">
-        <v>15.118518518518519</v>
+        <v>15</v>
       </c>
       <c r="D238" s="29">
         <v>5</v>
@@ -20883,7 +20883,7 @@
         <v>344</v>
       </c>
       <c r="C239" s="29">
-        <v>170.45945945945945</v>
+        <v>170</v>
       </c>
       <c r="D239" s="29">
         <v>1</v>
@@ -21031,7 +21031,7 @@
         <v>355</v>
       </c>
       <c r="C241" s="29">
-        <v>69.345454545454544</v>
+        <v>69</v>
       </c>
       <c r="D241" s="29">
         <v>1</v>
@@ -21327,7 +21327,7 @@
         <v>359</v>
       </c>
       <c r="C245" s="29">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D245" s="29">
         <v>5</v>
@@ -21401,7 +21401,7 @@
         <v>362</v>
       </c>
       <c r="C246" s="29">
-        <v>9.4444444444444446</v>
+        <v>9</v>
       </c>
       <c r="D246" s="29">
         <v>5</v>
@@ -21475,7 +21475,7 @@
         <v>352</v>
       </c>
       <c r="C247" s="29">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="D247" s="29">
         <v>5</v>
@@ -21549,7 +21549,7 @@
         <v>101</v>
       </c>
       <c r="C248" s="29">
-        <v>33.799999999999997</v>
+        <v>34</v>
       </c>
       <c r="D248" s="29">
         <v>4</v>
@@ -21771,7 +21771,7 @@
         <v>378</v>
       </c>
       <c r="C251" s="29">
-        <v>137.10526315789474</v>
+        <v>137</v>
       </c>
       <c r="D251" s="29">
         <v>1</v>
@@ -22141,7 +22141,7 @@
         <v>389</v>
       </c>
       <c r="C256" s="29">
-        <v>138.5</v>
+        <v>139</v>
       </c>
       <c r="D256" s="29">
         <v>1</v>
@@ -22215,7 +22215,7 @@
         <v>393</v>
       </c>
       <c r="C257" s="29">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="D257" s="29">
         <v>5</v>
@@ -22289,7 +22289,7 @@
         <v>399</v>
       </c>
       <c r="C258" s="29">
-        <v>20.583333333333332</v>
+        <v>21</v>
       </c>
       <c r="D258" s="29">
         <v>5</v>
@@ -22437,7 +22437,7 @@
         <v>55</v>
       </c>
       <c r="C260" s="29">
-        <v>28.333333333333332</v>
+        <v>28</v>
       </c>
       <c r="D260" s="29">
         <v>5</v>
@@ -22585,7 +22585,7 @@
         <v>61</v>
       </c>
       <c r="C262" s="29">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="D262" s="29">
         <v>5</v>
@@ -22659,7 +22659,7 @@
         <v>94</v>
       </c>
       <c r="C263" s="29">
-        <v>8.8000000000000007</v>
+        <v>9</v>
       </c>
       <c r="D263" s="29">
         <v>5</v>
@@ -23177,7 +23177,7 @@
         <v>131</v>
       </c>
       <c r="C270" s="29">
-        <v>20.688524590163933</v>
+        <v>21</v>
       </c>
       <c r="D270" s="29">
         <v>5</v>
@@ -23251,7 +23251,7 @@
         <v>139</v>
       </c>
       <c r="C271" s="29">
-        <v>11.285714285714286</v>
+        <v>11</v>
       </c>
       <c r="D271" s="29">
         <v>5</v>
@@ -23473,7 +23473,7 @@
         <v>156</v>
       </c>
       <c r="C274" s="29">
-        <v>42.607142857142854</v>
+        <v>43</v>
       </c>
       <c r="D274" s="29">
         <v>3</v>
@@ -23547,7 +23547,7 @@
         <v>167</v>
       </c>
       <c r="C275" s="29">
-        <v>50.285714285714285</v>
+        <v>50</v>
       </c>
       <c r="D275" s="29">
         <v>3</v>
@@ -23621,7 +23621,7 @@
         <v>180</v>
       </c>
       <c r="C276" s="29">
-        <v>51.956521739130437</v>
+        <v>52</v>
       </c>
       <c r="D276" s="29">
         <v>2</v>
@@ -23769,7 +23769,7 @@
         <v>191</v>
       </c>
       <c r="C278" s="29">
-        <v>64.7</v>
+        <v>65</v>
       </c>
       <c r="D278" s="29">
         <v>1</v>
@@ -23843,7 +23843,7 @@
         <v>182</v>
       </c>
       <c r="C279" s="29">
-        <v>15.3125</v>
+        <v>15</v>
       </c>
       <c r="D279" s="29">
         <v>5</v>
@@ -23991,7 +23991,7 @@
         <v>120</v>
       </c>
       <c r="C281" s="29">
-        <v>22.4</v>
+        <v>22</v>
       </c>
       <c r="D281" s="29">
         <v>5</v>
@@ -24139,7 +24139,7 @@
         <v>164</v>
       </c>
       <c r="C283" s="29">
-        <v>68.5</v>
+        <v>69</v>
       </c>
       <c r="D283" s="29">
         <v>1</v>
@@ -24435,7 +24435,7 @@
         <v>225</v>
       </c>
       <c r="C287" s="29">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D287" s="29">
         <v>5</v>
@@ -24509,7 +24509,7 @@
         <v>221</v>
       </c>
       <c r="C288" s="29">
-        <v>1.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="D288" s="29">
         <v>5</v>
@@ -24583,7 +24583,7 @@
         <v>227</v>
       </c>
       <c r="C289" s="29">
-        <v>44.416666666666664</v>
+        <v>44</v>
       </c>
       <c r="D289" s="29">
         <v>3</v>
@@ -24657,7 +24657,7 @@
         <v>228</v>
       </c>
       <c r="C290" s="29">
-        <v>17.263157894736842</v>
+        <v>17</v>
       </c>
       <c r="D290" s="29">
         <v>5</v>
@@ -24731,7 +24731,7 @@
         <v>234</v>
       </c>
       <c r="C291" s="29">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="D291" s="29">
         <v>5</v>
@@ -24805,7 +24805,7 @@
         <v>237</v>
       </c>
       <c r="C292" s="29">
-        <v>35.703703703703702</v>
+        <v>36</v>
       </c>
       <c r="D292" s="29">
         <v>4</v>
@@ -24879,7 +24879,7 @@
         <v>239</v>
       </c>
       <c r="C293" s="29">
-        <v>10.795454545454545</v>
+        <v>11</v>
       </c>
       <c r="D293" s="29">
         <v>5</v>
@@ -25101,7 +25101,7 @@
         <v>247</v>
       </c>
       <c r="C296" s="29">
-        <v>17.333333333333332</v>
+        <v>17</v>
       </c>
       <c r="D296" s="29">
         <v>5</v>
@@ -25175,7 +25175,7 @@
         <v>248</v>
       </c>
       <c r="C297" s="29">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="D297" s="29">
         <v>5</v>
@@ -25249,7 +25249,7 @@
         <v>253</v>
       </c>
       <c r="C298" s="29">
-        <v>52.189189189189186</v>
+        <v>52</v>
       </c>
       <c r="D298" s="29">
         <v>2</v>
@@ -25323,7 +25323,7 @@
         <v>256</v>
       </c>
       <c r="C299" s="29">
-        <v>36.75</v>
+        <v>37</v>
       </c>
       <c r="D299" s="29">
         <v>4</v>
@@ -25397,7 +25397,7 @@
         <v>260</v>
       </c>
       <c r="C300" s="29">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="D300" s="29">
         <v>5</v>
@@ -25471,7 +25471,7 @@
         <v>261</v>
       </c>
       <c r="C301" s="29">
-        <v>20.9375</v>
+        <v>21</v>
       </c>
       <c r="D301" s="29">
         <v>5</v>
@@ -25693,7 +25693,7 @@
         <v>275</v>
       </c>
       <c r="C304" s="29">
-        <v>15.875</v>
+        <v>16</v>
       </c>
       <c r="D304" s="29">
         <v>5</v>
@@ -25767,7 +25767,7 @@
         <v>276</v>
       </c>
       <c r="C305" s="29">
-        <v>13.842696629213483</v>
+        <v>14</v>
       </c>
       <c r="D305" s="29">
         <v>5</v>
@@ -25915,7 +25915,7 @@
         <v>279</v>
       </c>
       <c r="C307" s="29">
-        <v>28.91764705882353</v>
+        <v>29</v>
       </c>
       <c r="D307" s="29">
         <v>5</v>
@@ -25989,7 +25989,7 @@
         <v>281</v>
       </c>
       <c r="C308" s="29">
-        <v>17.086956521739129</v>
+        <v>17</v>
       </c>
       <c r="D308" s="29">
         <v>5</v>
@@ -26063,7 +26063,7 @@
         <v>223</v>
       </c>
       <c r="C309" s="29">
-        <v>35.81818181818182</v>
+        <v>36</v>
       </c>
       <c r="D309" s="29">
         <v>4</v>
@@ -26211,7 +26211,7 @@
         <v>300</v>
       </c>
       <c r="C311" s="29">
-        <v>15.521739130434783</v>
+        <v>16</v>
       </c>
       <c r="D311" s="29">
         <v>5</v>
@@ -26581,7 +26581,7 @@
         <v>318</v>
       </c>
       <c r="C316" s="29">
-        <v>14.7875</v>
+        <v>15</v>
       </c>
       <c r="D316" s="29">
         <v>5</v>
@@ -26655,7 +26655,7 @@
         <v>319</v>
       </c>
       <c r="C317" s="29">
-        <v>13.142857142857142</v>
+        <v>13</v>
       </c>
       <c r="D317" s="29">
         <v>5</v>
@@ -26951,7 +26951,7 @@
         <v>333</v>
       </c>
       <c r="C321" s="29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="D321" s="29">
         <v>5</v>
@@ -27099,7 +27099,7 @@
         <v>343</v>
       </c>
       <c r="C323" s="29">
-        <v>19.438596491228068</v>
+        <v>19</v>
       </c>
       <c r="D323" s="29">
         <v>5</v>
@@ -27173,7 +27173,7 @@
         <v>780</v>
       </c>
       <c r="C324" s="29">
-        <v>50.3125</v>
+        <v>50</v>
       </c>
       <c r="D324" s="29">
         <v>3</v>
@@ -27247,7 +27247,7 @@
         <v>782</v>
       </c>
       <c r="C325" s="29">
-        <v>17.24770642201835</v>
+        <v>17</v>
       </c>
       <c r="D325" s="29">
         <v>5</v>
@@ -27469,7 +27469,7 @@
         <v>788</v>
       </c>
       <c r="C328" s="29">
-        <v>18.36</v>
+        <v>18</v>
       </c>
       <c r="D328" s="29">
         <v>5</v>
@@ -27912,7 +27912,7 @@
       <c r="B334" s="28" t="s">
         <v>800</v>
       </c>
-      <c r="C334" s="30">
+      <c r="C334" s="29">
         <v>68</v>
       </c>
       <c r="D334" s="30">
@@ -28135,7 +28135,7 @@
         <v>806</v>
       </c>
       <c r="C337" s="29">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D337" s="29">
         <v>5</v>
@@ -28283,7 +28283,7 @@
         <v>810</v>
       </c>
       <c r="C339" s="29">
-        <v>14.166666666666666</v>
+        <v>14</v>
       </c>
       <c r="D339" s="29">
         <v>5</v>
@@ -28653,7 +28653,7 @@
         <v>820</v>
       </c>
       <c r="C344" s="29">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="D344" s="29">
         <v>5</v>
@@ -29171,7 +29171,7 @@
         <v>834</v>
       </c>
       <c r="C351" s="29">
-        <v>18.666666666666668</v>
+        <v>19</v>
       </c>
       <c r="D351" s="29">
         <v>5</v>
@@ -29392,7 +29392,7 @@
       <c r="B354" s="28" t="s">
         <v>840</v>
       </c>
-      <c r="C354" s="30">
+      <c r="C354" s="29">
         <v>10</v>
       </c>
       <c r="D354" s="30">
